--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4623,7 +4623,7 @@
         <v>117734516</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -4739,7 +4739,7 @@
         <v>121264511</v>
       </c>
       <c r="B38" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 47184-2019 artfynd.xlsx
+++ b/artfynd/A 47184-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4734,121 +4734,6 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>121264511</v>
-      </c>
-      <c r="B38" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Södra Håleberget, Ög</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>501348</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6495107</v>
-      </c>
-      <c r="S38" t="n">
-        <v>50</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Motala</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Motala</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>E-Mot-0232</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Daniel Hjelm</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
